--- a/backup/操作說明.xlsx
+++ b/backup/操作說明.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="19200" windowHeight="8080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="63">
   <si>
     <t>操作說明</t>
   </si>
@@ -101,7 +101,7 @@
     <t>架刀</t>
   </si>
   <si>
-    <t>按住L進入準備姿態，此時按下方向鍵可釋放對應劍術；劍術消耗2點TP，造成2點傷害；劍術命中BOSS可使 BOSS 短暫進入硬直狀態</t>
+    <t>按住L進入準備姿態，可抵禦來自正面的子彈攻擊，此時按下方向鍵可釋放對應劍術；劍術消耗2點TP，造成2點傷害；劍術命中BOSS可使BOSS短暫進入硬直狀態；釋放劍術期間角色處於無敵狀態</t>
   </si>
   <si>
     <t>L+方向上</t>
@@ -161,7 +161,52 @@
     <t>切換忍術</t>
   </si>
   <si>
-    <t>按照火焰、火球、稜刃、迴旋鏢的順序循環切換</t>
+    <t>按住I及對應方向鍵切換忍術</t>
+  </si>
+  <si>
+    <t>I+方向上</t>
+  </si>
+  <si>
+    <t>火焰</t>
+  </si>
+  <si>
+    <t>向前上方釋放三團火焰</t>
+  </si>
+  <si>
+    <t>I+方向下</t>
+  </si>
+  <si>
+    <t>火球</t>
+  </si>
+  <si>
+    <t>向前下方釋放三團火球</t>
+  </si>
+  <si>
+    <t>I+方向後</t>
+  </si>
+  <si>
+    <t>棱刃</t>
+  </si>
+  <si>
+    <t>向上下各釋放一個棱刃</t>
+  </si>
+  <si>
+    <t>I+方向前</t>
+  </si>
+  <si>
+    <t>迴旋鏢</t>
+  </si>
+  <si>
+    <t>向前方釋放一枚迴旋鏢</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>滅殺</t>
+  </si>
+  <si>
+    <t>按下H進行蓄力並消耗TP點數，釋放後發動強力攻擊；蓄力命中時，迅速連按H鍵，將依據蓄力期間消耗的TP點數發動連鎖斬擊，最多可連續斬擊9名敵人；連鎖斬擊期間角色處於無敵狀態</t>
   </si>
   <si>
     <t>O</t>
@@ -1205,12 +1250,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="3" width="12.625" customWidth="1"/>
-    <col min="4" max="4" width="17.75" customWidth="1"/>
-    <col min="5" max="5" width="27.125" customWidth="1"/>
+    <col min="1" max="3" width="12.6272727272727" customWidth="1"/>
+    <col min="4" max="4" width="17.7545454545455" customWidth="1"/>
+    <col min="5" max="5" width="32.4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="39" customHeight="1" spans="1:5">
@@ -1327,7 +1372,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" ht="83" customHeight="1" spans="1:5">
+    <row r="9" ht="89" customHeight="1" spans="1:5">
       <c r="A9" s="8" t="s">
         <v>22</v>
       </c>
@@ -1402,7 +1447,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" ht="50" customHeight="1" spans="1:5">
+    <row r="14" ht="20" customHeight="1" spans="1:5">
       <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
@@ -1417,48 +1462,123 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" ht="50" customHeight="1" spans="1:5">
-      <c r="A15" s="5" t="s">
+    <row r="15" ht="20" customHeight="1" spans="1:5">
+      <c r="A15" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="6" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="16" ht="50" customHeight="1" spans="1:5">
-      <c r="A16" s="5" t="s">
+    <row r="16" ht="20" customHeight="1" spans="1:5">
+      <c r="A16" s="9"/>
+      <c r="B16" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C16" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="5"/>
       <c r="D16" s="6" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
+    <row r="17" ht="20" customHeight="1" spans="1:5">
+      <c r="A17" s="9"/>
+      <c r="B17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1" spans="1:5">
+      <c r="A18" s="9"/>
+      <c r="B18" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1" spans="1:5">
+      <c r="A19" s="9"/>
+      <c r="B19" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" ht="97" customHeight="1" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" ht="50" customHeight="1" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="5"/>
+      <c r="D21" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:5">
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:5">
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="17">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
@@ -1470,10 +1590,12 @@
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A9:A13"/>
+    <mergeCell ref="A15:A19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/backup/操作說明.xlsx
+++ b/backup/操作說明.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Godot\GodotPro\NinjaGaiden_Return\backup\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8080"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -206,7 +211,7 @@
     <t>滅殺</t>
   </si>
   <si>
-    <t>按下H進行蓄力並消耗TP點數，釋放後發動強力攻擊；蓄力命中時，迅速連按H鍵，將依據蓄力期間消耗的TP點數發動連鎖斬擊，最多可連續斬擊9名敵人；連鎖斬擊期間角色處於無敵狀態</t>
+    <t>按下H進行蓄力並消耗TP點數，釋放後發動強力攻擊；蓄力命中時，迅速連按H鍵，將消耗TP點數發動連鎖斬擊；連鎖斬擊期間角色處於無敵狀態</t>
   </si>
   <si>
     <t>O</t>
@@ -1251,10 +1256,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="3" width="12.6272727272727" customWidth="1"/>
-    <col min="4" max="4" width="17.7545454545455" customWidth="1"/>
+    <col min="1" max="3" width="12.625" customWidth="1"/>
+    <col min="4" max="4" width="17.7583333333333" customWidth="1"/>
     <col min="5" max="5" width="32.4" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1567,12 +1572,12 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="1:5">
+    <row r="22" ht="14" customHeight="1" spans="1:5">
       <c r="A22" s="10"/>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
     </row>
-    <row r="23" customHeight="1" spans="1:5">
+    <row r="23" ht="14" customHeight="1" spans="1:5">
       <c r="A23" s="10"/>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>

--- a/backup/操作說明.xlsx
+++ b/backup/操作說明.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Godot\GodotPro\NinjaGaiden_Return\backup\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="19200" windowHeight="8080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -112,7 +107,7 @@
     <t>L+方向上</t>
   </si>
   <si>
-    <t>羅剎</t>
+    <t>翔鶴</t>
   </si>
   <si>
     <t>躍向空中並進行斬擊</t>
@@ -121,7 +116,7 @@
     <t>L+方向下</t>
   </si>
   <si>
-    <t>飛燕</t>
+    <t>落龍刃</t>
   </si>
   <si>
     <t>僅限空中</t>
@@ -1256,10 +1251,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="3" width="12.625" customWidth="1"/>
-    <col min="4" max="4" width="17.7583333333333" customWidth="1"/>
+    <col min="1" max="3" width="12.6272727272727" customWidth="1"/>
+    <col min="4" max="4" width="17.7545454545455" customWidth="1"/>
     <col min="5" max="5" width="32.4" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1572,12 +1567,12 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" ht="14" customHeight="1" spans="1:5">
+    <row r="22" customHeight="1" spans="1:5">
       <c r="A22" s="10"/>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
     </row>
-    <row r="23" ht="14" customHeight="1" spans="1:5">
+    <row r="23" customHeight="1" spans="1:5">
       <c r="A23" s="10"/>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>

--- a/backup/操作說明.xlsx
+++ b/backup/操作說明.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Godot\GodotPro\NinjaGaiden_Return\backup\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8080"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1251,10 +1256,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="3" width="12.6272727272727" customWidth="1"/>
-    <col min="4" max="4" width="17.7545454545455" customWidth="1"/>
+    <col min="1" max="3" width="12.625" customWidth="1"/>
+    <col min="4" max="4" width="17.7583333333333" customWidth="1"/>
     <col min="5" max="5" width="32.4" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1567,12 +1572,12 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="1:5">
+    <row r="22" ht="14" customHeight="1" spans="1:5">
       <c r="A22" s="10"/>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
     </row>
-    <row r="23" customHeight="1" spans="1:5">
+    <row r="23" ht="14" customHeight="1" spans="1:5">
       <c r="A23" s="10"/>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
